--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>125967234</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>125966509</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125966260</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125967234</v>
+        <v>125966509</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469599</v>
+        <v>469651</v>
       </c>
       <c r="R3" t="n">
-        <v>6698153</v>
+        <v>6698068</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>60 tal plantor koncentrerade på på en yta av 1*2 m. 3 blomstänglar.</t>
+          <t>Längst med stammarna på båda granarna</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>125966359</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125966509</v>
+        <v>125967234</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469651</v>
+        <v>469599</v>
       </c>
       <c r="R5" t="n">
-        <v>6698068</v>
+        <v>6698153</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Längst med stammarna på båda granarna</t>
+          <t>60 tal plantor koncentrerade på på en yta av 1*2 m. 3 blomstänglar.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 13323-2025 artfynd.xlsx
+++ b/artfynd/A 13323-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125966260</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125966509</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125966359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,8 +1140,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125967234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>